--- a/excel_routes/route_CAI_GIZ_threats.xlsx
+++ b/excel_routes/route_CAI_GIZ_threats.xlsx
@@ -5,10 +5,10 @@
   <workbookPr codeName="ThisWorkbook"/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_260726_at_14.46\reports\excel_routes\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="D:\CODERED\LAB\Artifacts\outputs\run_generated_270726_at_12.25\reports\excel_routes\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{9C45DC18-3405-4E9F-A6A0-F42523BB3C97}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{EE5EB988-7034-4D37-B75F-9CA0C297FC56}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
     <workbookView xWindow="12972" yWindow="348" windowWidth="10068" windowHeight="10284" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
@@ -25,7 +25,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="121" uniqueCount="38">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="126" uniqueCount="39">
   <si>
     <t>Date</t>
   </si>
@@ -85,6 +85,9 @@
   </si>
   <si>
     <t>08-AUG-26</t>
+  </si>
+  <si>
+    <t>13-AUG-26</t>
   </si>
   <si>
     <t>15-AUG-26</t>
@@ -535,7 +538,7 @@
 <file path=xl/worksheets/sheet1.xml><?xml version="1.0" encoding="utf-8"?>
 <worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" xmlns:xr2="http://schemas.microsoft.com/office/spreadsheetml/2015/revision2" xmlns:xr3="http://schemas.microsoft.com/office/spreadsheetml/2016/revision3" mc:Ignorable="x14ac xr xr2 xr3" xr:uid="{00000000-0001-0000-0000-000000000000}">
   <sheetPr codeName="Sheet1"/>
-  <dimension ref="A1:K23"/>
+  <dimension ref="A1:K24"/>
   <sheetFormatPr defaultRowHeight="14.4" x14ac:dyDescent="0.3"/>
   <cols>
     <col min="1" max="1" width="11" customWidth="1"/>
@@ -599,10 +602,10 @@
         <v>11590</v>
       </c>
       <c r="E2" s="2">
-        <v>14840</v>
+        <v>14839</v>
       </c>
       <c r="F2" s="2">
-        <v>-3250</v>
+        <v>-3249</v>
       </c>
       <c r="G2" s="2">
         <v>30</v>
@@ -704,10 +707,10 @@
         <v>12887</v>
       </c>
       <c r="E5" s="2">
-        <v>13147</v>
+        <v>13146</v>
       </c>
       <c r="F5" s="2">
-        <v>-260</v>
+        <v>-259</v>
       </c>
       <c r="G5" s="2">
         <v>30</v>
@@ -736,13 +739,13 @@
         <v>13</v>
       </c>
       <c r="D6" s="2">
-        <v>14881</v>
+        <v>13788</v>
       </c>
       <c r="E6" s="2">
-        <v>16833</v>
+        <v>13843</v>
       </c>
       <c r="F6" s="2">
-        <v>-1952</v>
+        <v>-55</v>
       </c>
       <c r="G6" s="2">
         <v>30</v>
@@ -771,13 +774,13 @@
         <v>13</v>
       </c>
       <c r="D7" s="2">
-        <v>13788</v>
+        <v>14880</v>
       </c>
       <c r="E7" s="2">
-        <v>13843</v>
+        <v>16832</v>
       </c>
       <c r="F7" s="2">
-        <v>-55</v>
+        <v>-1952</v>
       </c>
       <c r="G7" s="2">
         <v>30</v>
@@ -806,13 +809,13 @@
         <v>13</v>
       </c>
       <c r="D8" s="2">
-        <v>12887</v>
+        <v>13788</v>
       </c>
       <c r="E8" s="2">
-        <v>14840</v>
+        <v>13843</v>
       </c>
       <c r="F8" s="2">
-        <v>-1953</v>
+        <v>-55</v>
       </c>
       <c r="G8" s="2">
         <v>30</v>
@@ -841,13 +844,13 @@
         <v>13</v>
       </c>
       <c r="D9" s="2">
-        <v>10990</v>
+        <v>12887</v>
       </c>
       <c r="E9" s="2">
-        <v>11754</v>
+        <v>14839</v>
       </c>
       <c r="F9" s="2">
-        <v>-764</v>
+        <v>-1952</v>
       </c>
       <c r="G9" s="2">
         <v>30</v>
@@ -876,13 +879,13 @@
         <v>13</v>
       </c>
       <c r="D10" s="2">
-        <v>11590</v>
+        <v>10989</v>
       </c>
       <c r="E10" s="2">
-        <v>12450</v>
+        <v>11754</v>
       </c>
       <c r="F10" s="2">
-        <v>-860</v>
+        <v>-765</v>
       </c>
       <c r="G10" s="2">
         <v>30</v>
@@ -908,28 +911,28 @@
         <v>12</v>
       </c>
       <c r="C11" s="2" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D11" s="2">
-        <v>10148</v>
+        <v>11590</v>
       </c>
       <c r="E11" s="2">
-        <v>14840</v>
+        <v>12450</v>
       </c>
       <c r="F11" s="2">
-        <v>-4692</v>
+        <v>-860</v>
       </c>
       <c r="G11" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H11" s="2">
         <v>30</v>
       </c>
       <c r="I11" s="2">
-        <v>10</v>
-      </c>
-      <c r="J11" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J11" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="K11" s="2" t="s">
         <v>15</v>
@@ -937,34 +940,34 @@
     </row>
     <row r="12" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A12" s="2" t="s">
+        <v>26</v>
+      </c>
+      <c r="B12" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C12" s="2" t="s">
         <v>27</v>
       </c>
-      <c r="B12" s="2" t="s">
-        <v>12</v>
-      </c>
-      <c r="C12" s="2" t="s">
-        <v>13</v>
-      </c>
       <c r="D12" s="2">
-        <v>12887</v>
+        <v>10107</v>
       </c>
       <c r="E12" s="2">
-        <v>14840</v>
+        <v>14839</v>
       </c>
       <c r="F12" s="2">
-        <v>-1953</v>
+        <v>-4732</v>
       </c>
       <c r="G12" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H12" s="2">
         <v>30</v>
       </c>
       <c r="I12" s="2">
-        <v>0</v>
-      </c>
-      <c r="J12" s="4" t="s">
-        <v>17</v>
+        <v>10</v>
+      </c>
+      <c r="J12" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K12" s="2" t="s">
         <v>15</v>
@@ -978,28 +981,28 @@
         <v>12</v>
       </c>
       <c r="C13" s="2" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D13" s="2">
-        <v>10148</v>
+        <v>12887</v>
       </c>
       <c r="E13" s="2">
-        <v>14840</v>
+        <v>14839</v>
       </c>
       <c r="F13" s="2">
-        <v>-4692</v>
+        <v>-1952</v>
       </c>
       <c r="G13" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H13" s="2">
         <v>30</v>
       </c>
       <c r="I13" s="2">
-        <v>10</v>
-      </c>
-      <c r="J13" s="3" t="s">
-        <v>14</v>
+        <v>0</v>
+      </c>
+      <c r="J13" s="4" t="s">
+        <v>17</v>
       </c>
       <c r="K13" s="2" t="s">
         <v>15</v>
@@ -1013,25 +1016,25 @@
         <v>12</v>
       </c>
       <c r="C14" s="2" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D14" s="2">
-        <v>10990</v>
+        <v>10107</v>
       </c>
       <c r="E14" s="2">
-        <v>14840</v>
+        <v>14839</v>
       </c>
       <c r="F14" s="2">
-        <v>-3850</v>
+        <v>-4732</v>
       </c>
       <c r="G14" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H14" s="2">
         <v>30</v>
       </c>
       <c r="I14" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J14" s="3" t="s">
         <v>14</v>
@@ -1051,10 +1054,10 @@
         <v>13</v>
       </c>
       <c r="D15" s="2">
-        <v>10990</v>
+        <v>10989</v>
       </c>
       <c r="E15" s="2">
-        <v>14840</v>
+        <v>14839</v>
       </c>
       <c r="F15" s="2">
         <v>-3850</v>
@@ -1083,25 +1086,25 @@
         <v>12</v>
       </c>
       <c r="C16" s="2" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D16" s="2">
-        <v>9053</v>
+        <v>10989</v>
       </c>
       <c r="E16" s="2">
-        <v>14840</v>
+        <v>14839</v>
       </c>
       <c r="F16" s="2">
-        <v>-5787</v>
+        <v>-3850</v>
       </c>
       <c r="G16" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H16" s="2">
         <v>30</v>
       </c>
       <c r="I16" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J16" s="3" t="s">
         <v>14</v>
@@ -1118,25 +1121,25 @@
         <v>12</v>
       </c>
       <c r="C17" s="2" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D17" s="2">
-        <v>10990</v>
+        <v>9017</v>
       </c>
       <c r="E17" s="2">
-        <v>14840</v>
+        <v>14839</v>
       </c>
       <c r="F17" s="2">
-        <v>-3850</v>
+        <v>-5822</v>
       </c>
       <c r="G17" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H17" s="2">
         <v>30</v>
       </c>
       <c r="I17" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J17" s="3" t="s">
         <v>14</v>
@@ -1156,13 +1159,13 @@
         <v>13</v>
       </c>
       <c r="D18" s="2">
-        <v>10389</v>
+        <v>10989</v>
       </c>
       <c r="E18" s="2">
-        <v>14840</v>
+        <v>14839</v>
       </c>
       <c r="F18" s="2">
-        <v>-4451</v>
+        <v>-3850</v>
       </c>
       <c r="G18" s="2">
         <v>30</v>
@@ -1191,13 +1194,13 @@
         <v>13</v>
       </c>
       <c r="D19" s="2">
-        <v>9679</v>
+        <v>10389</v>
       </c>
       <c r="E19" s="2">
-        <v>10348</v>
+        <v>14839</v>
       </c>
       <c r="F19" s="2">
-        <v>-669</v>
+        <v>-4450</v>
       </c>
       <c r="G19" s="2">
         <v>30</v>
@@ -1208,8 +1211,8 @@
       <c r="I19" s="2">
         <v>0</v>
       </c>
-      <c r="J19" s="4" t="s">
-        <v>17</v>
+      <c r="J19" s="3" t="s">
+        <v>14</v>
       </c>
       <c r="K19" s="2" t="s">
         <v>15</v>
@@ -1229,10 +1232,10 @@
         <v>9679</v>
       </c>
       <c r="E20" s="2">
-        <v>11044</v>
+        <v>10348</v>
       </c>
       <c r="F20" s="2">
-        <v>-1365</v>
+        <v>-669</v>
       </c>
       <c r="G20" s="2">
         <v>30</v>
@@ -1258,25 +1261,25 @@
         <v>12</v>
       </c>
       <c r="C21" s="2" t="s">
-        <v>26</v>
+        <v>13</v>
       </c>
       <c r="D21" s="2">
-        <v>9053</v>
+        <v>9679</v>
       </c>
       <c r="E21" s="2">
         <v>11044</v>
       </c>
       <c r="F21" s="2">
-        <v>-1991</v>
+        <v>-1365</v>
       </c>
       <c r="G21" s="2">
-        <v>20</v>
+        <v>30</v>
       </c>
       <c r="H21" s="2">
         <v>30</v>
       </c>
       <c r="I21" s="2">
-        <v>10</v>
+        <v>0</v>
       </c>
       <c r="J21" s="4" t="s">
         <v>17</v>
@@ -1287,31 +1290,31 @@
     </row>
     <row r="22" spans="1:11" x14ac:dyDescent="0.3">
       <c r="A22" s="2" t="s">
-        <v>36</v>
+        <v>37</v>
       </c>
       <c r="B22" s="2" t="s">
         <v>12</v>
       </c>
       <c r="C22" s="2" t="s">
-        <v>13</v>
+        <v>27</v>
       </c>
       <c r="D22" s="2">
-        <v>9679</v>
+        <v>9017</v>
       </c>
       <c r="E22" s="2">
         <v>11044</v>
       </c>
       <c r="F22" s="2">
-        <v>-1365</v>
+        <v>-2027</v>
       </c>
       <c r="G22" s="2">
-        <v>30</v>
+        <v>20</v>
       </c>
       <c r="H22" s="2">
         <v>30</v>
       </c>
       <c r="I22" s="2">
-        <v>0</v>
+        <v>10</v>
       </c>
       <c r="J22" s="4" t="s">
         <v>17</v>
@@ -1352,6 +1355,41 @@
         <v>17</v>
       </c>
       <c r="K23" s="2" t="s">
+        <v>15</v>
+      </c>
+    </row>
+    <row r="24" spans="1:11" x14ac:dyDescent="0.3">
+      <c r="A24" s="2" t="s">
+        <v>38</v>
+      </c>
+      <c r="B24" s="2" t="s">
+        <v>12</v>
+      </c>
+      <c r="C24" s="2" t="s">
+        <v>13</v>
+      </c>
+      <c r="D24" s="2">
+        <v>9679</v>
+      </c>
+      <c r="E24" s="2">
+        <v>11044</v>
+      </c>
+      <c r="F24" s="2">
+        <v>-1365</v>
+      </c>
+      <c r="G24" s="2">
+        <v>30</v>
+      </c>
+      <c r="H24" s="2">
+        <v>30</v>
+      </c>
+      <c r="I24" s="2">
+        <v>0</v>
+      </c>
+      <c r="J24" s="4" t="s">
+        <v>17</v>
+      </c>
+      <c r="K24" s="2" t="s">
         <v>15</v>
       </c>
     </row>
